--- a/schema/ADRM/ADRM Conformance.xlsx
+++ b/schema/ADRM/ADRM Conformance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82cfe7acc6d68563/Documents/github/HL7-Validator/schema/ADRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="449" documentId="13_ncr:1_{ACE43B80-9608-4C70-9002-146B7E56DB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8B8DDFA-9D75-425D-9A23-371E6EEBBD77}"/>
+  <xr:revisionPtr revIDLastSave="520" documentId="13_ncr:1_{ACE43B80-9608-4C70-9002-146B7E56DB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{093D5E85-A889-4E97-A5EB-FCDE44F3615B}"/>
   <bookViews>
-    <workbookView xWindow="-6510" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{1F17C434-0E14-4C1A-8639-296F466D5A6B}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1F17C434-0E14-4C1A-8639-296F466D5A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="799">
   <si>
     <t>HL7au Identifier</t>
   </si>
@@ -3280,18 +3280,6 @@
     <t>No PDF/HTML/FT interpreter</t>
   </si>
   <si>
-    <t>No HTML interpreter</t>
-  </si>
-  <si>
-    <t>No PDF interpreter</t>
-  </si>
-  <si>
-    <t>No RTF interpreter</t>
-  </si>
-  <si>
-    <t>No FT interpeter</t>
-  </si>
-  <si>
     <t>Message only testing</t>
   </si>
   <si>
@@ -3374,6 +3362,36 @@
   </si>
   <si>
     <t>HL7 v2.XML Schema</t>
+  </si>
+  <si>
+    <t>Segment Rule/Parser Rule</t>
+  </si>
+  <si>
+    <t>No testing of FT data after rendering</t>
+  </si>
+  <si>
+    <t>Parser Rule</t>
+  </si>
+  <si>
+    <t>No image map testing</t>
+  </si>
+  <si>
+    <t>No CSS3 parser</t>
+  </si>
+  <si>
+    <t>No testing of Letter head</t>
+  </si>
+  <si>
+    <t>No testing of rendered data</t>
+  </si>
+  <si>
+    <t>Not testable</t>
+  </si>
+  <si>
+    <t>???There are no interactive Word Forms in RTF documents</t>
+  </si>
+  <si>
+    <t>???There are no watermarks in RTF documents</t>
   </si>
 </sst>
 </file>
@@ -3551,7 +3569,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3647,9 +3665,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4062,7 +4077,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="37" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -4076,7 +4091,7 @@
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -4116,7 +4131,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -4132,7 +4147,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -4176,7 +4191,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="37" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -4192,7 +4207,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -4300,7 +4315,7 @@
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="8" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -4358,7 +4373,7 @@
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="37" t="s">
         <v>44</v>
       </c>
       <c r="B22" s="9" t="s">
@@ -4374,11 +4389,11 @@
         <v>50</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="38"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="9"/>
       <c r="C23" s="15"/>
       <c r="D23" s="2" t="s">
@@ -4387,7 +4402,7 @@
       <c r="E23" s="9"/>
     </row>
     <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A24" s="38"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="9"/>
       <c r="C24" s="15"/>
       <c r="D24" s="2" t="s">
@@ -4396,7 +4411,7 @@
       <c r="E24" s="9"/>
     </row>
     <row r="25" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A25" s="38"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="9"/>
       <c r="C25" s="15"/>
       <c r="D25" s="2" t="s">
@@ -4405,7 +4420,7 @@
       <c r="E25" s="9"/>
     </row>
     <row r="26" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A26" s="38"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="9"/>
       <c r="C26" s="15"/>
       <c r="D26" s="2" t="s">
@@ -4428,7 +4443,7 @@
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="8" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -4446,7 +4461,7 @@
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="8" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -4464,7 +4479,7 @@
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="8" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -4486,7 +4501,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="37" t="s">
         <v>59</v>
       </c>
       <c r="B31" s="9" t="s">
@@ -4500,7 +4515,7 @@
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -4572,7 +4587,7 @@
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="8" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -4633,7 +4648,7 @@
       <c r="F40" s="13"/>
     </row>
     <row r="41" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A41" s="33" t="s">
+      <c r="A41" s="19" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="12" t="s">
@@ -4645,7 +4660,7 @@
       <c r="F41" s="12"/>
     </row>
     <row r="42" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>79</v>
       </c>
       <c r="B42" s="9" t="s">
@@ -4659,11 +4674,11 @@
       </c>
       <c r="E42" s="9"/>
       <c r="F42" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="31" t="s">
         <v>81</v>
       </c>
       <c r="B43" s="9" t="s">
@@ -4677,11 +4692,11 @@
       </c>
       <c r="E43" s="9"/>
       <c r="F43" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="31" t="s">
         <v>83</v>
       </c>
       <c r="B44" s="9" t="s">
@@ -4695,23 +4710,20 @@
       </c>
       <c r="E44" s="9"/>
       <c r="F44" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="9"/>
       <c r="C45" s="15"/>
       <c r="D45" s="2" t="s">
         <v>85</v>
       </c>
       <c r="E45" s="9"/>
-      <c r="F45" t="s">
-        <v>761</v>
-      </c>
     </row>
     <row r="46" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A46" s="30" t="s">
+      <c r="A46" s="31" t="s">
         <v>86</v>
       </c>
       <c r="B46" s="9" t="s">
@@ -4725,23 +4737,20 @@
       </c>
       <c r="E46" s="9"/>
       <c r="F46" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="9"/>
       <c r="C47" s="15"/>
       <c r="D47" s="2" t="s">
         <v>88</v>
       </c>
       <c r="E47" s="9"/>
-      <c r="F47" t="s">
-        <v>761</v>
-      </c>
     </row>
     <row r="48" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="31" t="s">
         <v>89</v>
       </c>
       <c r="B48" s="9" t="s">
@@ -4755,11 +4764,11 @@
       </c>
       <c r="E48" s="9"/>
       <c r="F48" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="9"/>
       <c r="C49" s="15"/>
       <c r="D49" s="2" t="s">
@@ -4768,7 +4777,7 @@
       <c r="E49" s="9"/>
     </row>
     <row r="50" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A50" s="30"/>
+      <c r="A50" s="31"/>
       <c r="B50" s="9"/>
       <c r="C50" s="15"/>
       <c r="D50" s="2" t="s">
@@ -4777,7 +4786,7 @@
       <c r="E50" s="9"/>
     </row>
     <row r="51" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="9"/>
       <c r="C51" s="15"/>
       <c r="D51" s="2" t="s">
@@ -4786,7 +4795,7 @@
       <c r="E51" s="9"/>
     </row>
     <row r="52" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="9"/>
       <c r="C52" s="15"/>
       <c r="D52" s="2" t="s">
@@ -4795,7 +4804,7 @@
       <c r="E52" s="9"/>
     </row>
     <row r="53" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="9"/>
       <c r="C53" s="15"/>
       <c r="D53" s="2" t="s">
@@ -4804,7 +4813,7 @@
       <c r="E53" s="9"/>
     </row>
     <row r="54" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="9"/>
       <c r="C54" s="15"/>
       <c r="D54" s="2" t="s">
@@ -4813,7 +4822,7 @@
       <c r="E54" s="9"/>
     </row>
     <row r="55" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="9"/>
       <c r="C55" s="15"/>
       <c r="D55" s="2" t="s">
@@ -4836,7 +4845,7 @@
       </c>
       <c r="E56" s="9"/>
       <c r="F56" t="s">
-        <v>761</v>
+        <v>792</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -4854,11 +4863,11 @@
       </c>
       <c r="E57" s="9"/>
       <c r="F57" t="s">
-        <v>761</v>
+        <v>793</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>102</v>
       </c>
       <c r="B58" s="9" t="s">
@@ -4872,7 +4881,7 @@
       </c>
       <c r="E58" s="9"/>
       <c r="F58" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -4890,7 +4899,7 @@
       </c>
       <c r="E59" s="9"/>
       <c r="F59" t="s">
-        <v>761</v>
+        <v>794</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -4908,7 +4917,7 @@
       </c>
       <c r="E60" s="9"/>
       <c r="F60" t="s">
-        <v>761</v>
+        <v>794</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -4926,7 +4935,7 @@
       </c>
       <c r="E61" s="9"/>
       <c r="F61" t="s">
-        <v>761</v>
+        <v>794</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -4944,7 +4953,7 @@
       </c>
       <c r="E62" s="9"/>
       <c r="F62" t="s">
-        <v>761</v>
+        <v>795</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -4962,11 +4971,11 @@
       </c>
       <c r="E63" s="9"/>
       <c r="F63" t="s">
-        <v>761</v>
+        <v>795</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="31" t="s">
         <v>114</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -4980,7 +4989,7 @@
       </c>
       <c r="E64" s="9"/>
       <c r="F64" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5000,7 +5009,7 @@
         <v>118</v>
       </c>
       <c r="F65" t="s">
-        <v>761</v>
+        <v>795</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -5016,7 +5025,7 @@
       <c r="F66" s="12"/>
     </row>
     <row r="67" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A67" s="38" t="s">
+      <c r="A67" s="37" t="s">
         <v>121</v>
       </c>
       <c r="B67" s="9" t="s">
@@ -5030,11 +5039,11 @@
       </c>
       <c r="E67" s="9"/>
       <c r="F67" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A68" s="38" t="s">
+      <c r="A68" s="37" t="s">
         <v>124</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -5048,11 +5057,11 @@
       </c>
       <c r="E68" s="9"/>
       <c r="F68" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A69" s="38" t="s">
+      <c r="A69" s="37" t="s">
         <v>125</v>
       </c>
       <c r="B69" s="9" t="s">
@@ -5066,11 +5075,11 @@
       </c>
       <c r="E69" s="9"/>
       <c r="F69" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A70" s="38" t="s">
+      <c r="A70" s="37" t="s">
         <v>127</v>
       </c>
       <c r="B70" s="9" t="s">
@@ -5084,11 +5093,11 @@
       </c>
       <c r="E70" s="9"/>
       <c r="F70" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A71" s="38" t="s">
+      <c r="A71" s="37" t="s">
         <v>129</v>
       </c>
       <c r="B71" s="9" t="s">
@@ -5102,11 +5111,11 @@
       </c>
       <c r="E71" s="9"/>
       <c r="F71" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A72" s="38" t="s">
+      <c r="A72" s="37" t="s">
         <v>131</v>
       </c>
       <c r="B72" s="9" t="s">
@@ -5120,11 +5129,11 @@
       </c>
       <c r="E72" s="9"/>
       <c r="F72" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A73" s="38" t="s">
+      <c r="A73" s="37" t="s">
         <v>133</v>
       </c>
       <c r="B73" s="9" t="s">
@@ -5138,11 +5147,11 @@
       </c>
       <c r="E73" s="9"/>
       <c r="F73" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A74" s="38" t="s">
+      <c r="A74" s="37" t="s">
         <v>135</v>
       </c>
       <c r="B74" s="9" t="s">
@@ -5158,11 +5167,11 @@
         <v>137</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A75" s="38" t="s">
+      <c r="A75" s="37" t="s">
         <v>138</v>
       </c>
       <c r="B75" s="9" t="s">
@@ -5178,11 +5187,11 @@
         <v>140</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A76" s="38" t="s">
+      <c r="A76" s="37" t="s">
         <v>141</v>
       </c>
       <c r="B76" s="9" t="s">
@@ -5198,7 +5207,7 @@
         <v>140</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5226,13 +5235,13 @@
       <c r="F78" s="12"/>
     </row>
     <row r="79" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A79" s="30" t="s">
+      <c r="A79" s="31" t="s">
         <v>147</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="36" t="s">
         <v>16</v>
       </c>
       <c r="D79" s="9" t="s">
@@ -5240,11 +5249,11 @@
       </c>
       <c r="E79" s="9"/>
       <c r="F79" s="9" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A80" s="30" t="s">
+      <c r="A80" s="31" t="s">
         <v>148</v>
       </c>
       <c r="B80" s="9" t="s">
@@ -5258,11 +5267,11 @@
       </c>
       <c r="E80" s="9"/>
       <c r="F80" s="9" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A81" s="30" t="s">
+      <c r="A81" s="31" t="s">
         <v>150</v>
       </c>
       <c r="B81" s="9" t="s">
@@ -5276,11 +5285,11 @@
       </c>
       <c r="E81" s="9"/>
       <c r="F81" s="9" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A82" s="30" t="s">
+      <c r="A82" s="31" t="s">
         <v>152</v>
       </c>
       <c r="B82" s="9" t="s">
@@ -5294,11 +5303,11 @@
       </c>
       <c r="E82" s="9"/>
       <c r="F82" s="9" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A83" s="30" t="s">
+      <c r="A83" s="31" t="s">
         <v>154</v>
       </c>
       <c r="B83" s="9" t="s">
@@ -5312,11 +5321,11 @@
       </c>
       <c r="E83" s="9"/>
       <c r="F83" s="9" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A84" s="30" t="s">
+      <c r="A84" s="31" t="s">
         <v>156</v>
       </c>
       <c r="B84" s="9" t="s">
@@ -5330,7 +5339,7 @@
       </c>
       <c r="E84" s="9"/>
       <c r="F84" s="9" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5348,7 +5357,7 @@
       </c>
       <c r="E85" s="9"/>
       <c r="F85" s="9" t="s">
-        <v>762</v>
+        <v>796</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5366,7 +5375,7 @@
       </c>
       <c r="E86" s="9"/>
       <c r="F86" s="9" t="s">
-        <v>762</v>
+        <v>796</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5384,7 +5393,7 @@
       </c>
       <c r="E87" s="9"/>
       <c r="F87" s="9" t="s">
-        <v>762</v>
+        <v>796</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -5400,7 +5409,7 @@
       <c r="F88" s="12"/>
     </row>
     <row r="89" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A89" s="38" t="s">
+      <c r="A89" s="37" t="s">
         <v>166</v>
       </c>
       <c r="B89" s="9" t="s">
@@ -5414,11 +5423,11 @@
       </c>
       <c r="E89" s="9"/>
       <c r="F89" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A90" s="38" t="s">
+      <c r="A90" s="37" t="s">
         <v>168</v>
       </c>
       <c r="B90" s="9" t="s">
@@ -5432,11 +5441,11 @@
       </c>
       <c r="E90" s="9"/>
       <c r="F90" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A91" s="38" t="s">
+      <c r="A91" s="37" t="s">
         <v>170</v>
       </c>
       <c r="B91" s="9" t="s">
@@ -5450,11 +5459,11 @@
       </c>
       <c r="E91" s="9"/>
       <c r="F91" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A92" s="38" t="s">
+      <c r="A92" s="37" t="s">
         <v>172</v>
       </c>
       <c r="B92" s="9" t="s">
@@ -5468,11 +5477,11 @@
       </c>
       <c r="E92" s="9"/>
       <c r="F92" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A93" s="38" t="s">
+      <c r="A93" s="37" t="s">
         <v>174</v>
       </c>
       <c r="B93" s="9" t="s">
@@ -5486,11 +5495,11 @@
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A94" s="38" t="s">
+      <c r="A94" s="37" t="s">
         <v>176</v>
       </c>
       <c r="B94" s="9" t="s">
@@ -5504,7 +5513,7 @@
       </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5532,7 +5541,7 @@
       <c r="F96" s="12"/>
     </row>
     <row r="97" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A97" s="30" t="s">
+      <c r="A97" s="31" t="s">
         <v>182</v>
       </c>
       <c r="B97" s="9" t="s">
@@ -5546,11 +5555,11 @@
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A98" s="30" t="s">
+      <c r="A98" s="31" t="s">
         <v>184</v>
       </c>
       <c r="B98" s="9" t="s">
@@ -5564,11 +5573,11 @@
       </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A99" s="30" t="s">
+      <c r="A99" s="31" t="s">
         <v>186</v>
       </c>
       <c r="B99" s="9" t="s">
@@ -5582,11 +5591,11 @@
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A100" s="30" t="s">
+      <c r="A100" s="31" t="s">
         <v>188</v>
       </c>
       <c r="B100" s="9" t="s">
@@ -5600,11 +5609,11 @@
       </c>
       <c r="E100" s="9"/>
       <c r="F100" s="9" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A101" s="30" t="s">
+      <c r="A101" s="31" t="s">
         <v>190</v>
       </c>
       <c r="B101" s="9" t="s">
@@ -5618,11 +5627,11 @@
       </c>
       <c r="E101" s="9"/>
       <c r="F101" s="9" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A102" s="30" t="s">
+      <c r="A102" s="31" t="s">
         <v>192</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -5636,11 +5645,11 @@
       </c>
       <c r="E102" s="9"/>
       <c r="F102" s="9" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A103" s="30" t="s">
+      <c r="A103" s="31" t="s">
         <v>194</v>
       </c>
       <c r="B103" s="9" t="s">
@@ -5654,7 +5663,7 @@
       </c>
       <c r="E103" s="9"/>
       <c r="F103" s="9" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5672,7 +5681,7 @@
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5689,8 +5698,8 @@
         <v>199</v>
       </c>
       <c r="E105" s="9"/>
-      <c r="F105" s="9" t="s">
-        <v>763</v>
+      <c r="F105" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5708,7 +5717,7 @@
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9" t="s">
-        <v>763</v>
+        <v>796</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5726,7 +5735,7 @@
       </c>
       <c r="E107" s="9"/>
       <c r="F107" s="9" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -5744,7 +5753,7 @@
       </c>
       <c r="E108" s="9"/>
       <c r="F108" s="9" t="s">
-        <v>763</v>
+        <v>796</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -5760,7 +5769,7 @@
       <c r="F109" s="12"/>
     </row>
     <row r="110" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A110" s="38" t="s">
+      <c r="A110" s="37" t="s">
         <v>208</v>
       </c>
       <c r="B110" s="9" t="s">
@@ -5776,11 +5785,11 @@
         <v>210</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A111" s="38" t="s">
+      <c r="A111" s="37" t="s">
         <v>211</v>
       </c>
       <c r="B111" s="9" t="s">
@@ -5794,11 +5803,11 @@
       </c>
       <c r="E111" s="9"/>
       <c r="F111" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A112" s="38" t="s">
+      <c r="A112" s="37" t="s">
         <v>213</v>
       </c>
       <c r="B112" s="9" t="s">
@@ -5812,11 +5821,11 @@
       </c>
       <c r="E112" s="9"/>
       <c r="F112" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A113" s="38" t="s">
+      <c r="A113" s="37" t="s">
         <v>215</v>
       </c>
       <c r="B113" s="9" t="s">
@@ -5830,11 +5839,11 @@
       </c>
       <c r="E113" s="9"/>
       <c r="F113" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A114" s="38" t="s">
+      <c r="A114" s="37" t="s">
         <v>217</v>
       </c>
       <c r="B114" s="9" t="s">
@@ -5848,11 +5857,11 @@
       </c>
       <c r="E114" s="9"/>
       <c r="F114" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A115" s="38" t="s">
+      <c r="A115" s="37" t="s">
         <v>219</v>
       </c>
       <c r="B115" s="9" t="s">
@@ -5866,11 +5875,11 @@
       </c>
       <c r="E115" s="9"/>
       <c r="F115" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A116" s="38" t="s">
+      <c r="A116" s="37" t="s">
         <v>221</v>
       </c>
       <c r="B116" s="9" t="s">
@@ -5884,11 +5893,11 @@
       </c>
       <c r="E116" s="9"/>
       <c r="F116" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A117" s="38" t="s">
+      <c r="A117" s="37" t="s">
         <v>223</v>
       </c>
       <c r="B117" s="9" t="s">
@@ -5902,11 +5911,11 @@
       </c>
       <c r="E117" s="9"/>
       <c r="F117" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A118" s="38" t="s">
+      <c r="A118" s="37" t="s">
         <v>225</v>
       </c>
       <c r="B118" s="9" t="s">
@@ -5922,11 +5931,11 @@
         <v>227</v>
       </c>
       <c r="F118" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A119" s="38" t="s">
+      <c r="A119" s="37" t="s">
         <v>228</v>
       </c>
       <c r="B119" s="9" t="s">
@@ -5940,11 +5949,11 @@
       </c>
       <c r="E119" s="9"/>
       <c r="F119" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A120" s="38" t="s">
+      <c r="A120" s="37" t="s">
         <v>230</v>
       </c>
       <c r="B120" s="9" t="s">
@@ -5958,11 +5967,11 @@
       </c>
       <c r="E120" s="9"/>
       <c r="F120" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A121" s="38" t="s">
+      <c r="A121" s="37" t="s">
         <v>232</v>
       </c>
       <c r="B121" s="9" t="s">
@@ -5978,11 +5987,11 @@
         <v>234</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A122" s="38" t="s">
+      <c r="A122" s="37" t="s">
         <v>235</v>
       </c>
       <c r="B122" s="9" t="s">
@@ -5996,7 +6005,7 @@
       </c>
       <c r="E122" s="9"/>
       <c r="F122" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6024,7 +6033,7 @@
       <c r="F124" s="12"/>
     </row>
     <row r="125" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A125" s="30" t="s">
+      <c r="A125" s="37" t="s">
         <v>241</v>
       </c>
       <c r="B125" s="9" t="s">
@@ -6038,11 +6047,11 @@
       </c>
       <c r="E125" s="9"/>
       <c r="F125" s="9" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A126" s="30" t="s">
+      <c r="A126" s="37" t="s">
         <v>243</v>
       </c>
       <c r="B126" s="9" t="s">
@@ -6056,11 +6065,11 @@
       </c>
       <c r="E126" s="9"/>
       <c r="F126" s="9" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A127" s="30" t="s">
+      <c r="A127" s="37" t="s">
         <v>245</v>
       </c>
       <c r="B127" s="9" t="s">
@@ -6074,11 +6083,11 @@
       </c>
       <c r="E127" s="9"/>
       <c r="F127" s="9" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A128" s="30" t="s">
+      <c r="A128" s="37" t="s">
         <v>247</v>
       </c>
       <c r="B128" s="9" t="s">
@@ -6092,11 +6101,11 @@
       </c>
       <c r="E128" s="9"/>
       <c r="F128" s="9" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A129" s="30" t="s">
+      <c r="A129" s="37" t="s">
         <v>249</v>
       </c>
       <c r="B129" s="9" t="s">
@@ -6110,11 +6119,11 @@
       </c>
       <c r="E129" s="9"/>
       <c r="F129" s="9" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A130" s="30" t="s">
+      <c r="A130" s="37" t="s">
         <v>251</v>
       </c>
       <c r="B130" s="9" t="s">
@@ -6128,7 +6137,7 @@
       </c>
       <c r="E130" s="9"/>
       <c r="F130" s="9" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6146,11 +6155,11 @@
       </c>
       <c r="E131" s="9"/>
       <c r="F131" s="9" t="s">
-        <v>764</v>
+        <v>790</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A132" s="30" t="s">
+      <c r="A132" s="31" t="s">
         <v>255</v>
       </c>
       <c r="B132" s="9" t="s">
@@ -6164,11 +6173,11 @@
       </c>
       <c r="E132" s="9"/>
       <c r="F132" s="9" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A133" s="30" t="s">
+      <c r="A133" s="31" t="s">
         <v>256</v>
       </c>
       <c r="B133" s="9" t="s">
@@ -6182,11 +6191,11 @@
       </c>
       <c r="E133" s="9"/>
       <c r="F133" s="9" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A134" s="30" t="s">
+      <c r="A134" s="31" t="s">
         <v>257</v>
       </c>
       <c r="B134" s="9" t="s">
@@ -6200,11 +6209,11 @@
       </c>
       <c r="E134" s="9"/>
       <c r="F134" s="9" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A135" s="30" t="s">
+      <c r="A135" s="31" t="s">
         <v>258</v>
       </c>
       <c r="B135" s="9" t="s">
@@ -6218,7 +6227,7 @@
       </c>
       <c r="E135" s="9"/>
       <c r="F135" s="9" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6236,11 +6245,11 @@
       </c>
       <c r="E136" s="9"/>
       <c r="F136" s="9" t="s">
-        <v>764</v>
+        <v>790</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A137" s="30" t="s">
+      <c r="A137" s="31" t="s">
         <v>261</v>
       </c>
       <c r="B137" s="9" t="s">
@@ -6254,11 +6263,11 @@
       </c>
       <c r="E137" s="9"/>
       <c r="F137" s="9" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A138" s="30" t="s">
+      <c r="A138" s="31" t="s">
         <v>262</v>
       </c>
       <c r="B138" s="9" t="s">
@@ -6272,7 +6281,7 @@
       </c>
       <c r="E138" s="9"/>
       <c r="F138" s="9" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -6288,7 +6297,7 @@
       <c r="F139" s="12"/>
     </row>
     <row r="140" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A140" s="38" t="s">
+      <c r="A140" s="37" t="s">
         <v>265</v>
       </c>
       <c r="B140" s="9" t="s">
@@ -6302,11 +6311,11 @@
       </c>
       <c r="E140" s="9"/>
       <c r="F140" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A141" s="38" t="s">
+      <c r="A141" s="37" t="s">
         <v>267</v>
       </c>
       <c r="B141" s="9" t="s">
@@ -6320,11 +6329,11 @@
       </c>
       <c r="E141" s="9"/>
       <c r="F141" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A142" s="38" t="s">
+      <c r="A142" s="37" t="s">
         <v>269</v>
       </c>
       <c r="B142" s="9" t="s">
@@ -6338,11 +6347,11 @@
       </c>
       <c r="E142" s="9"/>
       <c r="F142" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A143" s="38" t="s">
+      <c r="A143" s="37" t="s">
         <v>271</v>
       </c>
       <c r="B143" s="9" t="s">
@@ -6356,11 +6365,11 @@
       </c>
       <c r="E143" s="9"/>
       <c r="F143" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A144" s="38" t="s">
+      <c r="A144" s="37" t="s">
         <v>273</v>
       </c>
       <c r="B144" s="9" t="s">
@@ -6374,11 +6383,11 @@
       </c>
       <c r="E144" s="9"/>
       <c r="F144" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A145" s="38" t="s">
+      <c r="A145" s="37" t="s">
         <v>275</v>
       </c>
       <c r="B145" s="9" t="s">
@@ -6392,11 +6401,11 @@
       </c>
       <c r="E145" s="9"/>
       <c r="F145" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A146" s="38" t="s">
+      <c r="A146" s="37" t="s">
         <v>277</v>
       </c>
       <c r="B146" s="9" t="s">
@@ -6410,11 +6419,11 @@
       </c>
       <c r="E146" s="9"/>
       <c r="F146" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A147" s="38" t="s">
+      <c r="A147" s="37" t="s">
         <v>279</v>
       </c>
       <c r="B147" s="9" t="s">
@@ -6428,11 +6437,11 @@
       </c>
       <c r="E147" s="9"/>
       <c r="F147" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A148" s="38" t="s">
+      <c r="A148" s="37" t="s">
         <v>281</v>
       </c>
       <c r="B148" s="9" t="s">
@@ -6446,11 +6455,11 @@
       </c>
       <c r="E148" s="9"/>
       <c r="F148" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A149" s="38" t="s">
+      <c r="A149" s="37" t="s">
         <v>283</v>
       </c>
       <c r="B149" s="9" t="s">
@@ -6464,11 +6473,11 @@
       </c>
       <c r="E149" s="9"/>
       <c r="F149" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A150" s="38" t="s">
+      <c r="A150" s="37" t="s">
         <v>285</v>
       </c>
       <c r="B150" s="9" t="s">
@@ -6482,11 +6491,11 @@
       </c>
       <c r="E150" s="9"/>
       <c r="F150" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A151" s="38" t="s">
+      <c r="A151" s="37" t="s">
         <v>287</v>
       </c>
       <c r="B151" s="9" t="s">
@@ -6500,11 +6509,11 @@
       </c>
       <c r="E151" s="9"/>
       <c r="F151" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A152" s="38" t="s">
+      <c r="A152" s="37" t="s">
         <v>288</v>
       </c>
       <c r="B152" s="9" t="s">
@@ -6518,11 +6527,11 @@
       </c>
       <c r="E152" s="9"/>
       <c r="F152" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A153" s="38" t="s">
+      <c r="A153" s="37" t="s">
         <v>290</v>
       </c>
       <c r="B153" s="9" t="s">
@@ -6536,11 +6545,11 @@
       </c>
       <c r="E153" s="9"/>
       <c r="F153" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A154" s="38" t="s">
+      <c r="A154" s="37" t="s">
         <v>292</v>
       </c>
       <c r="B154" s="9" t="s">
@@ -6554,11 +6563,11 @@
       </c>
       <c r="E154" s="9"/>
       <c r="F154" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A155" s="38" t="s">
+      <c r="A155" s="37" t="s">
         <v>294</v>
       </c>
       <c r="B155" s="9" t="s">
@@ -6572,11 +6581,11 @@
       </c>
       <c r="E155" s="9"/>
       <c r="F155" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A156" s="38" t="s">
+      <c r="A156" s="37" t="s">
         <v>296</v>
       </c>
       <c r="B156" s="9" t="s">
@@ -6590,7 +6599,7 @@
       </c>
       <c r="E156" s="9"/>
       <c r="F156" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6606,7 +6615,7 @@
       <c r="F157" s="13"/>
     </row>
     <row r="158" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A158" s="38" t="s">
+      <c r="A158" s="37" t="s">
         <v>300</v>
       </c>
       <c r="B158" s="9" t="s">
@@ -6622,11 +6631,11 @@
         <v>303</v>
       </c>
       <c r="F158" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A159" s="38" t="s">
+      <c r="A159" s="37" t="s">
         <v>304</v>
       </c>
       <c r="B159" s="9" t="s">
@@ -6640,7 +6649,7 @@
       </c>
       <c r="E159" s="9"/>
       <c r="F159" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6658,7 +6667,7 @@
       </c>
       <c r="E160" s="15"/>
       <c r="F160" s="9" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6676,7 +6685,7 @@
       </c>
       <c r="E161" s="9"/>
       <c r="F161" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6694,7 +6703,7 @@
       </c>
       <c r="E162" s="9"/>
       <c r="F162" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6724,11 +6733,11 @@
       </c>
       <c r="E164" s="9"/>
       <c r="F164" s="9" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A165" s="38" t="s">
+      <c r="A165" s="37" t="s">
         <v>315</v>
       </c>
       <c r="B165" s="9" t="s">
@@ -6742,7 +6751,7 @@
       </c>
       <c r="E165" s="9"/>
       <c r="F165" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6760,11 +6769,11 @@
       </c>
       <c r="E166" s="9"/>
       <c r="F166" s="9" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A167" s="38" t="s">
+      <c r="A167" s="37" t="s">
         <v>319</v>
       </c>
       <c r="B167" s="9" t="s">
@@ -6778,7 +6787,7 @@
       </c>
       <c r="E167" s="9"/>
       <c r="F167" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6796,11 +6805,11 @@
       </c>
       <c r="E168" s="9"/>
       <c r="F168" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A169" s="34" t="s">
+      <c r="A169" s="33" t="s">
         <v>323</v>
       </c>
       <c r="B169" s="2" t="s">
@@ -6814,7 +6823,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6843,7 +6852,7 @@
       </c>
       <c r="E171" s="9"/>
       <c r="F171" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6861,7 +6870,7 @@
       </c>
       <c r="E172" s="9"/>
       <c r="F172" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6879,7 +6888,7 @@
       </c>
       <c r="E173" s="9"/>
       <c r="F173" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6897,7 +6906,7 @@
       </c>
       <c r="E174" s="9"/>
       <c r="F174" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -6915,7 +6924,7 @@
       </c>
       <c r="E175" s="9"/>
       <c r="F175" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -6943,11 +6952,11 @@
       </c>
       <c r="E177" s="9"/>
       <c r="F177" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A178" s="38" t="s">
+      <c r="A178" s="37" t="s">
         <v>339</v>
       </c>
       <c r="B178" s="9" t="s">
@@ -6961,11 +6970,11 @@
       </c>
       <c r="E178" s="9"/>
       <c r="F178" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A179" s="38" t="s">
+      <c r="A179" s="37" t="s">
         <v>342</v>
       </c>
       <c r="B179" s="9" t="s">
@@ -6979,7 +6988,7 @@
       </c>
       <c r="E179" s="9"/>
       <c r="F179" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -6997,7 +7006,7 @@
       </c>
       <c r="E180" s="9"/>
       <c r="F180" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7015,7 +7024,7 @@
       </c>
       <c r="E181" s="9"/>
       <c r="F181" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -7033,7 +7042,7 @@
       </c>
       <c r="E182" s="9"/>
       <c r="F182" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -7051,11 +7060,11 @@
       </c>
       <c r="E183" s="9"/>
       <c r="F183" s="9" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A184" s="40" t="s">
+      <c r="A184" s="39" t="s">
         <v>350</v>
       </c>
       <c r="B184" s="2" t="s">
@@ -7069,7 +7078,7 @@
       </c>
       <c r="E184" s="2"/>
       <c r="F184" s="9" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7087,7 +7096,7 @@
       </c>
       <c r="E185" s="9"/>
       <c r="F185" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7105,7 +7114,7 @@
       </c>
       <c r="E186" s="9"/>
       <c r="F186" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -7123,7 +7132,7 @@
       </c>
       <c r="E187" s="9"/>
       <c r="F187" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7141,7 +7150,7 @@
       </c>
       <c r="E188" s="9"/>
       <c r="F188" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7159,11 +7168,11 @@
       </c>
       <c r="E189" s="9"/>
       <c r="F189" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A190" s="38" t="s">
+      <c r="A190" s="37" t="s">
         <v>358</v>
       </c>
       <c r="B190" s="9" t="s">
@@ -7177,7 +7186,7 @@
       </c>
       <c r="E190" s="9"/>
       <c r="F190" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7195,7 +7204,7 @@
       </c>
       <c r="E191" s="9"/>
       <c r="F191" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -7225,7 +7234,7 @@
       </c>
       <c r="E193" s="9"/>
       <c r="F193" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7243,7 +7252,7 @@
       </c>
       <c r="E194" s="9"/>
       <c r="F194" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -7261,11 +7270,11 @@
       </c>
       <c r="E195" s="9"/>
       <c r="F195" s="9" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A196" s="38" t="s">
+      <c r="A196" s="37" t="s">
         <v>369</v>
       </c>
       <c r="B196" s="9" t="s">
@@ -7281,7 +7290,7 @@
         <v>371</v>
       </c>
       <c r="F196" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7409,7 +7418,7 @@
       </c>
     </row>
     <row r="205" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A205" s="38" t="s">
+      <c r="A205" s="37" t="s">
         <v>387</v>
       </c>
       <c r="B205" s="9" t="s">
@@ -7423,7 +7432,7 @@
       </c>
       <c r="E205" s="9"/>
       <c r="F205" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7514,7 +7523,7 @@
       <c r="F211" s="8"/>
     </row>
     <row r="212" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A212" s="38" t="s">
+      <c r="A212" s="37" t="s">
         <v>399</v>
       </c>
       <c r="B212" s="9" t="s">
@@ -7530,7 +7539,7 @@
         <v>401</v>
       </c>
       <c r="F212" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7598,7 +7607,7 @@
       </c>
       <c r="E216" s="9"/>
       <c r="F216" s="8" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7628,7 +7637,7 @@
       </c>
       <c r="E218" s="9"/>
       <c r="F218" s="8" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -7645,7 +7654,7 @@
         <v>743</v>
       </c>
       <c r="E219" s="9"/>
-      <c r="F219" s="35" t="s">
+      <c r="F219" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7664,7 +7673,7 @@
       </c>
       <c r="E220" s="9"/>
       <c r="F220" s="8" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -7683,17 +7692,17 @@
       <c r="A222" s="30" t="s">
         <v>420</v>
       </c>
-      <c r="B222" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C222" s="37" t="s">
+      <c r="B222" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C222" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D222" s="36" t="s">
+      <c r="D222" s="35" t="s">
         <v>421</v>
       </c>
       <c r="E222" s="9"/>
-      <c r="F222" s="35" t="s">
+      <c r="F222" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7701,17 +7710,17 @@
       <c r="A223" s="30" t="s">
         <v>422</v>
       </c>
-      <c r="B223" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C223" s="37" t="s">
+      <c r="B223" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C223" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D223" s="36" t="s">
+      <c r="D223" s="35" t="s">
         <v>423</v>
       </c>
       <c r="E223" s="9"/>
-      <c r="F223" s="35" t="s">
+      <c r="F223" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7719,17 +7728,17 @@
       <c r="A224" s="30" t="s">
         <v>424</v>
       </c>
-      <c r="B224" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C224" s="37" t="s">
+      <c r="B224" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C224" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D224" s="36" t="s">
+      <c r="D224" s="35" t="s">
         <v>425</v>
       </c>
       <c r="E224" s="9"/>
-      <c r="F224" s="35" t="s">
+      <c r="F224" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7737,17 +7746,17 @@
       <c r="A225" s="30" t="s">
         <v>426</v>
       </c>
-      <c r="B225" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C225" s="37" t="s">
+      <c r="B225" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C225" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D225" s="36" t="s">
+      <c r="D225" s="35" t="s">
         <v>427</v>
       </c>
       <c r="E225" s="9"/>
-      <c r="F225" s="35" t="s">
+      <c r="F225" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7778,7 +7787,7 @@
       </c>
       <c r="E227" s="9"/>
       <c r="F227" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7795,7 +7804,7 @@
         <v>433</v>
       </c>
       <c r="E228" s="9"/>
-      <c r="F228" s="35" t="s">
+      <c r="F228" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7813,7 +7822,7 @@
         <v>435</v>
       </c>
       <c r="E229" s="9"/>
-      <c r="F229" s="35" t="s">
+      <c r="F229" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7831,7 +7840,7 @@
         <v>437</v>
       </c>
       <c r="E230" s="9"/>
-      <c r="F230" s="35" t="s">
+      <c r="F230" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7849,7 +7858,7 @@
         <v>427</v>
       </c>
       <c r="E231" s="9"/>
-      <c r="F231" s="35" t="s">
+      <c r="F231" s="34" t="s">
         <v>755</v>
       </c>
     </row>
@@ -7879,8 +7888,8 @@
         <v>442</v>
       </c>
       <c r="E233" s="9"/>
-      <c r="F233" s="35" t="s">
-        <v>775</v>
+      <c r="F233" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -7897,8 +7906,8 @@
         <v>444</v>
       </c>
       <c r="E234" s="9"/>
-      <c r="F234" s="35" t="s">
-        <v>775</v>
+      <c r="F234" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -7916,7 +7925,7 @@
       </c>
       <c r="E235" s="9"/>
       <c r="F235" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -7933,8 +7942,8 @@
         <v>448</v>
       </c>
       <c r="E236" s="9"/>
-      <c r="F236" s="35" t="s">
-        <v>775</v>
+      <c r="F236" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -7951,8 +7960,8 @@
         <v>450</v>
       </c>
       <c r="E237" s="9"/>
-      <c r="F237" s="35" t="s">
-        <v>775</v>
+      <c r="F237" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -7969,8 +7978,8 @@
         <v>452</v>
       </c>
       <c r="E238" s="9"/>
-      <c r="F238" s="35" t="s">
-        <v>775</v>
+      <c r="F238" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -7988,7 +7997,7 @@
       </c>
       <c r="E239" s="9"/>
       <c r="F239" s="9" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8005,8 +8014,8 @@
         <v>456</v>
       </c>
       <c r="E240" s="9"/>
-      <c r="F240" s="35" t="s">
-        <v>775</v>
+      <c r="F240" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="241" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8035,8 +8044,8 @@
         <v>460</v>
       </c>
       <c r="E242" s="9"/>
-      <c r="F242" s="35" t="s">
-        <v>775</v>
+      <c r="F242" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8053,8 +8062,8 @@
         <v>462</v>
       </c>
       <c r="E243" s="9"/>
-      <c r="F243" s="35" t="s">
-        <v>775</v>
+      <c r="F243" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8072,7 +8081,7 @@
       </c>
       <c r="E244" s="9"/>
       <c r="F244" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8089,8 +8098,8 @@
         <v>450</v>
       </c>
       <c r="E245" s="9"/>
-      <c r="F245" s="35" t="s">
-        <v>775</v>
+      <c r="F245" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="246" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8107,8 +8116,8 @@
         <v>452</v>
       </c>
       <c r="E246" s="9"/>
-      <c r="F246" s="35" t="s">
-        <v>775</v>
+      <c r="F246" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -8126,7 +8135,7 @@
       </c>
       <c r="E247" s="9"/>
       <c r="F247" s="9" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8155,8 +8164,8 @@
         <v>442</v>
       </c>
       <c r="E249" s="9"/>
-      <c r="F249" s="35" t="s">
-        <v>775</v>
+      <c r="F249" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="250" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8173,8 +8182,8 @@
         <v>462</v>
       </c>
       <c r="E250" s="9"/>
-      <c r="F250" s="35" t="s">
-        <v>775</v>
+      <c r="F250" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="251" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8192,7 +8201,7 @@
       </c>
       <c r="E251" s="9"/>
       <c r="F251" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="252" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8209,8 +8218,8 @@
         <v>450</v>
       </c>
       <c r="E252" s="9"/>
-      <c r="F252" s="35" t="s">
-        <v>775</v>
+      <c r="F252" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8227,8 +8236,8 @@
         <v>452</v>
       </c>
       <c r="E253" s="9"/>
-      <c r="F253" s="35" t="s">
-        <v>775</v>
+      <c r="F253" s="34" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -8246,7 +8255,7 @@
       </c>
       <c r="E254" s="9"/>
       <c r="F254" s="9" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8276,7 +8285,7 @@
       </c>
       <c r="E256" s="9"/>
       <c r="F256" s="8" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="257" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8294,7 +8303,7 @@
       </c>
       <c r="E257" s="9"/>
       <c r="F257" s="8" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="258" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8312,7 +8321,7 @@
       </c>
       <c r="E258" s="9"/>
       <c r="F258" s="9" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="259" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8330,7 +8339,7 @@
       </c>
       <c r="E259" s="9"/>
       <c r="F259" s="9" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8348,7 +8357,7 @@
       </c>
       <c r="E260" s="9"/>
       <c r="F260" s="8" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="261" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8366,7 +8375,7 @@
       </c>
       <c r="E261" s="9"/>
       <c r="F261" s="8" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="262" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8396,7 +8405,7 @@
       </c>
       <c r="E263" s="9"/>
       <c r="F263" s="9" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="264" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8438,7 +8447,7 @@
       </c>
       <c r="E266" s="9"/>
       <c r="F266" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="267" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8456,7 +8465,7 @@
       </c>
       <c r="E267" s="9"/>
       <c r="F267" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="268" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8474,7 +8483,7 @@
       </c>
       <c r="E268" s="9"/>
       <c r="F268" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8492,7 +8501,7 @@
       </c>
       <c r="E269" s="9"/>
       <c r="F269" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="270" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8510,7 +8519,7 @@
       </c>
       <c r="E270" s="9"/>
       <c r="F270" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="271" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8528,7 +8537,7 @@
       </c>
       <c r="E271" s="9"/>
       <c r="F271" s="9" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="272" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8544,7 +8553,7 @@
       <c r="F272" s="12"/>
     </row>
     <row r="273" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A273" s="38" t="s">
+      <c r="A273" s="37" t="s">
         <v>512</v>
       </c>
       <c r="B273" s="9" t="s">
@@ -8558,11 +8567,11 @@
       </c>
       <c r="E273" s="9"/>
       <c r="F273" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="274" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A274" s="38" t="s">
+      <c r="A274" s="37" t="s">
         <v>514</v>
       </c>
       <c r="B274" s="9" t="s">
@@ -8576,11 +8585,11 @@
       </c>
       <c r="E274" s="9"/>
       <c r="F274" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="275" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A275" s="38" t="s">
+      <c r="A275" s="37" t="s">
         <v>516</v>
       </c>
       <c r="B275" s="9" t="s">
@@ -8594,7 +8603,7 @@
       </c>
       <c r="E275" s="9"/>
       <c r="F275" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="276" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8636,7 +8645,7 @@
       </c>
       <c r="E278" s="9"/>
       <c r="F278" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="279" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8654,7 +8663,7 @@
       </c>
       <c r="E279" s="9"/>
       <c r="F279" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="280" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8672,7 +8681,7 @@
       </c>
       <c r="E280" s="9"/>
       <c r="F280" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="281" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -8690,7 +8699,7 @@
       </c>
       <c r="E281" s="9"/>
       <c r="F281" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="282" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8708,7 +8717,7 @@
       </c>
       <c r="E282" s="9"/>
       <c r="F282" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8726,11 +8735,11 @@
       </c>
       <c r="E283" s="9"/>
       <c r="F283" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="284" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A284" s="38" t="s">
+      <c r="A284" s="37" t="s">
         <v>534</v>
       </c>
       <c r="B284" s="9" t="s">
@@ -8746,7 +8755,7 @@
         <v>371</v>
       </c>
       <c r="F284" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="285" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8776,7 +8785,7 @@
       </c>
       <c r="E286" s="9"/>
       <c r="F286" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="287" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8794,7 +8803,7 @@
       </c>
       <c r="E287" s="9"/>
       <c r="F287" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="288" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8812,7 +8821,7 @@
       </c>
       <c r="E288" s="9"/>
       <c r="F288" s="9" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="289" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8828,7 +8837,7 @@
       <c r="F289" s="13"/>
     </row>
     <row r="290" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A290" s="38" t="s">
+      <c r="A290" s="37" t="s">
         <v>544</v>
       </c>
       <c r="B290" s="9" t="s">
@@ -8842,11 +8851,11 @@
       </c>
       <c r="E290" s="9"/>
       <c r="F290" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="291" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A291" s="38" t="s">
+      <c r="A291" s="37" t="s">
         <v>546</v>
       </c>
       <c r="B291" s="9" t="s">
@@ -8860,11 +8869,11 @@
       </c>
       <c r="E291" s="9"/>
       <c r="F291" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="292" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A292" s="38" t="s">
+      <c r="A292" s="37" t="s">
         <v>548</v>
       </c>
       <c r="B292" s="9" t="s">
@@ -8878,11 +8887,11 @@
       </c>
       <c r="E292" s="9"/>
       <c r="F292" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="293" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A293" s="38" t="s">
+      <c r="A293" s="37" t="s">
         <v>550</v>
       </c>
       <c r="B293" s="9" t="s">
@@ -8896,11 +8905,11 @@
       </c>
       <c r="E293" s="9"/>
       <c r="F293" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="294" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A294" s="38" t="s">
+      <c r="A294" s="37" t="s">
         <v>552</v>
       </c>
       <c r="B294" s="9" t="s">
@@ -8914,7 +8923,7 @@
       </c>
       <c r="E294" s="9"/>
       <c r="F294" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="295" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -8954,7 +8963,7 @@
       </c>
     </row>
     <row r="297" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A297" s="38" t="s">
+      <c r="A297" s="37" t="s">
         <v>557</v>
       </c>
       <c r="B297" s="9" t="s">
@@ -8968,11 +8977,11 @@
       </c>
       <c r="E297" s="9"/>
       <c r="F297" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="298" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A298" s="38" t="s">
+      <c r="A298" s="37" t="s">
         <v>560</v>
       </c>
       <c r="B298" s="9" t="s">
@@ -8986,7 +8995,7 @@
       </c>
       <c r="E298" s="9"/>
       <c r="F298" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="299" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9028,7 +9037,7 @@
       </c>
       <c r="E301" s="9"/>
       <c r="F301" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="302" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9046,7 +9055,7 @@
       </c>
       <c r="E302" s="9"/>
       <c r="F302" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="303" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9064,7 +9073,7 @@
       </c>
       <c r="E303" s="9"/>
       <c r="F303" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="304" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9082,7 +9091,7 @@
       </c>
       <c r="E304" s="9"/>
       <c r="F304" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="305" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9102,7 +9111,7 @@
         <v>576</v>
       </c>
       <c r="F305" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="306" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9118,7 +9127,7 @@
       <c r="F306" s="12"/>
     </row>
     <row r="307" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A307" s="38" t="s">
+      <c r="A307" s="37" t="s">
         <v>579</v>
       </c>
       <c r="B307" s="9" t="s">
@@ -9132,11 +9141,11 @@
       </c>
       <c r="E307" s="9"/>
       <c r="F307" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="308" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A308" s="38" t="s">
+      <c r="A308" s="37" t="s">
         <v>581</v>
       </c>
       <c r="B308" s="9" t="s">
@@ -9150,11 +9159,11 @@
       </c>
       <c r="E308" s="9"/>
       <c r="F308" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="309" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A309" s="38" t="s">
+      <c r="A309" s="37" t="s">
         <v>583</v>
       </c>
       <c r="B309" s="9" t="s">
@@ -9168,11 +9177,11 @@
       </c>
       <c r="E309" s="9"/>
       <c r="F309" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="310" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A310" s="38" t="s">
+      <c r="A310" s="37" t="s">
         <v>585</v>
       </c>
       <c r="B310" s="9" t="s">
@@ -9186,11 +9195,11 @@
       </c>
       <c r="E310" s="9"/>
       <c r="F310" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="311" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A311" s="38" t="s">
+      <c r="A311" s="37" t="s">
         <v>587</v>
       </c>
       <c r="B311" s="9" t="s">
@@ -9204,7 +9213,7 @@
       </c>
       <c r="E311" s="9"/>
       <c r="F311" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="312" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9222,11 +9231,11 @@
       </c>
       <c r="E312" s="9"/>
       <c r="F312" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="313" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A313" s="38" t="s">
+      <c r="A313" s="37" t="s">
         <v>591</v>
       </c>
       <c r="B313" s="9" t="s">
@@ -9242,11 +9251,11 @@
         <v>593</v>
       </c>
       <c r="F313" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="314" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A314" s="38" t="s">
+      <c r="A314" s="37" t="s">
         <v>594</v>
       </c>
       <c r="B314" s="9" t="s">
@@ -9262,11 +9271,11 @@
         <v>593</v>
       </c>
       <c r="F314" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="315" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A315" s="38" t="s">
+      <c r="A315" s="37" t="s">
         <v>596</v>
       </c>
       <c r="B315" s="9" t="s">
@@ -9282,7 +9291,7 @@
         <v>598</v>
       </c>
       <c r="F315" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="316" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9300,7 +9309,7 @@
       </c>
       <c r="E316" s="9"/>
       <c r="F316" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="317" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9318,7 +9327,7 @@
       </c>
       <c r="E317" s="9"/>
       <c r="F317" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="318" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -9336,7 +9345,7 @@
       </c>
       <c r="E318" s="9"/>
       <c r="F318" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="319" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -9354,7 +9363,7 @@
       </c>
       <c r="E319" s="9"/>
       <c r="F319" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="320" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -9374,7 +9383,7 @@
         <v>609</v>
       </c>
       <c r="F320" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="321" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9392,7 +9401,7 @@
       </c>
       <c r="E321" s="9"/>
       <c r="F321" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="322" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9412,25 +9421,25 @@
         <v>614</v>
       </c>
       <c r="F322" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="323" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A323" s="31" t="s">
         <v>615</v>
       </c>
-      <c r="B323" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C323" s="37" t="s">
+      <c r="B323" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C323" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D323" s="36" t="s">
+      <c r="D323" s="35" t="s">
         <v>616</v>
       </c>
-      <c r="E323" s="36"/>
+      <c r="E323" s="35"/>
       <c r="F323" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="324" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9448,7 +9457,7 @@
       </c>
       <c r="E324" s="9"/>
       <c r="F324" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="325" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9466,7 +9475,7 @@
       </c>
       <c r="E325" s="9"/>
       <c r="F325" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="326" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9496,7 +9505,7 @@
       </c>
       <c r="E327" s="9"/>
       <c r="F327" s="9" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="328" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9514,7 +9523,7 @@
       </c>
       <c r="E328" s="9"/>
       <c r="F328" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="329" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9532,7 +9541,7 @@
       </c>
       <c r="E329" s="9"/>
       <c r="F329" s="9" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
     </row>
     <row r="330" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9550,7 +9559,7 @@
       </c>
       <c r="E330" s="9"/>
       <c r="F330" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="331" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9584,11 +9593,11 @@
       </c>
       <c r="E332" s="9"/>
       <c r="F332" s="9" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="333" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A333" s="38" t="s">
+      <c r="A333" s="37" t="s">
         <v>636</v>
       </c>
       <c r="B333" s="9" t="s">
@@ -9602,11 +9611,11 @@
       </c>
       <c r="E333" s="9"/>
       <c r="F333" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="334" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A334" s="38" t="s">
+      <c r="A334" s="37" t="s">
         <v>638</v>
       </c>
       <c r="B334" s="9" t="s">
@@ -9622,7 +9631,7 @@
         <v>640</v>
       </c>
       <c r="F334" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="335" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9640,7 +9649,7 @@
       </c>
       <c r="E335" s="9"/>
       <c r="F335" s="9" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="336" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9658,7 +9667,7 @@
       </c>
       <c r="E336" s="9"/>
       <c r="F336" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="337" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9678,7 +9687,7 @@
         <v>647</v>
       </c>
       <c r="F337" s="9" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="338" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9698,7 +9707,7 @@
         <v>647</v>
       </c>
       <c r="F338" s="9" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="339" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -9716,7 +9725,7 @@
       </c>
       <c r="E339" s="9"/>
       <c r="F339" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="340" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -9736,7 +9745,7 @@
         <v>654</v>
       </c>
       <c r="F340" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="341" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -9756,11 +9765,11 @@
         <v>654</v>
       </c>
       <c r="F341" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="342" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A342" s="38" t="s">
+      <c r="A342" s="37" t="s">
         <v>657</v>
       </c>
       <c r="B342" s="9" t="s">
@@ -9774,7 +9783,7 @@
       </c>
       <c r="E342" s="9"/>
       <c r="F342" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="343" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9792,11 +9801,11 @@
       </c>
       <c r="E343" s="9"/>
       <c r="F343" s="9" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="344" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A344" s="38" t="s">
+      <c r="A344" s="37" t="s">
         <v>661</v>
       </c>
       <c r="B344" s="9" t="s">
@@ -9810,11 +9819,11 @@
       </c>
       <c r="E344" s="9"/>
       <c r="F344" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="345" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A345" s="38" t="s">
+      <c r="A345" s="37" t="s">
         <v>663</v>
       </c>
       <c r="B345" s="9" t="s">
@@ -9828,7 +9837,7 @@
       </c>
       <c r="E345" s="9"/>
       <c r="F345" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="346" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9846,7 +9855,7 @@
       </c>
       <c r="E346" s="9"/>
       <c r="F346" s="9" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="347" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -9864,7 +9873,7 @@
       </c>
       <c r="E347" s="9"/>
       <c r="F347" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="348" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -9882,11 +9891,11 @@
       </c>
       <c r="E348" s="9"/>
       <c r="F348" s="9" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="349" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A349" s="38" t="s">
+      <c r="A349" s="37" t="s">
         <v>671</v>
       </c>
       <c r="B349" s="9" t="s">
@@ -9900,11 +9909,11 @@
       </c>
       <c r="E349" s="9"/>
       <c r="F349" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="350" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A350" s="38" t="s">
+      <c r="A350" s="37" t="s">
         <v>673</v>
       </c>
       <c r="B350" s="9" t="s">
@@ -9918,11 +9927,11 @@
       </c>
       <c r="E350" s="9"/>
       <c r="F350" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="351" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A351" s="38" t="s">
+      <c r="A351" s="37" t="s">
         <v>675</v>
       </c>
       <c r="B351" s="9" t="s">
@@ -9936,11 +9945,11 @@
       </c>
       <c r="E351" s="9"/>
       <c r="F351" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="352" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A352" s="39" t="s">
+      <c r="A352" s="38" t="s">
         <v>677</v>
       </c>
       <c r="B352" s="9" t="s">
@@ -9954,11 +9963,11 @@
       </c>
       <c r="E352" s="9"/>
       <c r="F352" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="353" spans="1:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="A353" s="38" t="s">
+      <c r="A353" s="37" t="s">
         <v>678</v>
       </c>
       <c r="B353" s="9" t="s">
@@ -9972,7 +9981,7 @@
       </c>
       <c r="E353" s="9"/>
       <c r="F353" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="354" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -9990,7 +9999,7 @@
       </c>
       <c r="E354" s="9"/>
       <c r="F354" s="9" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="355" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -10008,7 +10017,7 @@
       </c>
       <c r="E355" s="9"/>
       <c r="F355" s="9" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="356" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -10026,7 +10035,7 @@
       </c>
       <c r="E356" s="9"/>
       <c r="F356" s="9" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="357" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
@@ -10044,7 +10053,7 @@
       </c>
       <c r="E357" s="9"/>
       <c r="F357" s="9" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="358" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -10062,7 +10071,7 @@
       </c>
       <c r="E358" s="9"/>
       <c r="F358" s="9" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="359" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -10080,11 +10089,11 @@
       </c>
       <c r="E359" s="9"/>
       <c r="F359" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="360" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A360" s="38" t="s">
+      <c r="A360" s="37" t="s">
         <v>687</v>
       </c>
       <c r="B360" s="9" t="s">
@@ -10098,7 +10107,7 @@
       </c>
       <c r="E360" s="9"/>
       <c r="F360" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="361" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -10116,11 +10125,11 @@
       </c>
       <c r="E361" s="9"/>
       <c r="F361" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="362" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A362" s="38" t="s">
+      <c r="A362" s="37" t="s">
         <v>692</v>
       </c>
       <c r="B362" s="9" t="s">
@@ -10134,11 +10143,11 @@
       </c>
       <c r="E362" s="9"/>
       <c r="F362" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="363" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A363" s="40" t="s">
+      <c r="A363" s="39" t="s">
         <v>694</v>
       </c>
       <c r="B363" s="2" t="s">
@@ -10152,7 +10161,7 @@
       </c>
       <c r="E363" s="2"/>
       <c r="F363" s="9" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="364" spans="1:6" ht="33" x14ac:dyDescent="0.45">
@@ -10170,7 +10179,7 @@
       </c>
       <c r="E364" s="9"/>
       <c r="F364" s="9" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="365" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -10190,7 +10199,7 @@
         <v>698</v>
       </c>
       <c r="F365" s="9" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="366" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -10208,7 +10217,7 @@
       </c>
       <c r="E366" s="9"/>
       <c r="F366" s="9" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="367" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -10226,7 +10235,7 @@
       </c>
       <c r="E367" s="9"/>
       <c r="F367" s="9" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="368" spans="1:6" ht="16.5" x14ac:dyDescent="0.45">
@@ -10244,7 +10253,7 @@
       </c>
       <c r="E368" s="9"/>
       <c r="F368" s="9" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="369" spans="1:6" ht="49.5" x14ac:dyDescent="0.45">
